--- a/hr_toolkit/templates/archive_company_template.xlsx
+++ b/hr_toolkit/templates/archive_company_template.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14880"/>
+    <workbookView windowHeight="22140"/>
   </bookViews>
   <sheets>
     <sheet name="公司1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>公司1人员档案编号表</t>
   </si>
@@ -145,25 +145,29 @@
   <si>
     <t>离职申请单</t>
   </si>
+  <si>
+    <t>离职时间</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="8">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="yyyymmdd"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -171,14 +175,14 @@
       <b/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -186,7 +190,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -194,7 +198,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -202,14 +206,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -217,7 +221,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -225,7 +229,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -233,7 +237,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -241,7 +245,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -249,14 +253,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -264,7 +268,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -272,7 +276,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -280,14 +284,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -295,42 +299,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -661,165 +665,176 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -828,7 +843,7 @@
     <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -837,66 +852,60 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -1161,7 +1170,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1170,6 +1179,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1203,7 +1213,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1212,6 +1222,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1245,7 +1256,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1254,6 +1265,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1287,7 +1299,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1296,6 +1308,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1329,7 +1342,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1338,6 +1351,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1371,7 +1385,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1380,6 +1394,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1413,7 +1428,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1422,6 +1437,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1455,7 +1471,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1464,6 +1480,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1497,7 +1514,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1506,6 +1523,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1539,7 +1557,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1548,6 +1566,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1581,7 +1600,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1590,6 +1609,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1623,7 +1643,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1632,6 +1652,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1665,7 +1686,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1674,6 +1695,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1707,7 +1729,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1716,6 +1738,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1749,7 +1772,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1758,6 +1781,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1791,7 +1815,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1800,6 +1824,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1833,7 +1858,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1842,6 +1867,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1875,7 +1901,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1884,6 +1910,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1917,7 +1944,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1926,6 +1953,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -1959,7 +1987,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1968,6 +1996,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2001,7 +2030,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2010,6 +2039,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2043,7 +2073,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2052,6 +2082,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2085,7 +2116,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2094,6 +2125,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2127,7 +2159,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2136,6 +2168,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2169,7 +2202,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2178,6 +2211,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2211,7 +2245,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2220,6 +2254,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2253,7 +2288,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2262,6 +2297,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2295,7 +2331,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2304,6 +2340,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2337,7 +2374,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2346,6 +2383,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2379,7 +2417,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2388,6 +2426,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2421,7 +2460,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2430,6 +2469,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2463,7 +2503,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2472,6 +2512,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2505,7 +2546,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2514,6 +2555,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2547,7 +2589,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2556,6 +2598,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2589,7 +2632,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2598,6 +2641,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2631,7 +2675,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2640,6 +2684,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2673,7 +2718,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2682,6 +2727,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2715,7 +2761,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2724,6 +2770,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2757,7 +2804,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2766,6 +2813,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2799,7 +2847,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2808,6 +2856,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2841,7 +2890,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2850,6 +2899,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2883,7 +2933,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2892,6 +2942,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2925,7 +2976,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2934,6 +2985,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2967,7 +3019,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2976,6 +3028,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3009,7 +3062,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3018,6 +3071,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3051,7 +3105,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3060,6 +3114,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3093,7 +3148,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="365760"/>
+          <a:off x="3752850" y="365760"/>
           <a:ext cx="12700" cy="153035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3102,6 +3157,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3135,7 +3191,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="365760"/>
+          <a:off x="3752850" y="365760"/>
           <a:ext cx="141605" cy="13970"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3144,6 +3200,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3177,7 +3234,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3186,6 +3243,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3219,7 +3277,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3228,6 +3286,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3261,7 +3320,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3270,6 +3329,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3303,7 +3363,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3312,6 +3372,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3345,7 +3406,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3354,6 +3415,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3387,7 +3449,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3396,6 +3458,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3429,7 +3492,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3438,6 +3501,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3471,7 +3535,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3480,6 +3544,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3513,7 +3578,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="365760"/>
+          <a:off x="3752850" y="365760"/>
           <a:ext cx="12700" cy="153035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3522,6 +3587,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3555,7 +3621,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="365760"/>
+          <a:off x="3752850" y="365760"/>
           <a:ext cx="141605" cy="13970"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3564,6 +3630,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3597,7 +3664,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3606,6 +3673,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3639,7 +3707,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3648,6 +3716,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3681,7 +3750,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3690,6 +3759,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3723,7 +3793,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3732,6 +3802,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3765,7 +3836,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3774,6 +3845,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3807,7 +3879,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3816,6 +3888,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3849,7 +3922,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3858,6 +3931,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3891,7 +3965,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3900,6 +3974,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3933,7 +4008,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3942,6 +4017,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3975,7 +4051,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3984,6 +4060,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4017,7 +4094,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4026,6 +4103,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4059,7 +4137,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4068,6 +4146,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4101,7 +4180,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4110,6 +4189,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4143,7 +4223,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4152,6 +4232,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4185,7 +4266,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4194,6 +4275,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4227,7 +4309,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4236,6 +4318,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4269,7 +4352,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4278,6 +4361,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4311,7 +4395,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4320,6 +4404,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4353,7 +4438,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4362,6 +4447,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4395,7 +4481,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4404,6 +4490,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4437,7 +4524,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4446,6 +4533,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4479,7 +4567,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4488,6 +4576,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4521,7 +4610,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="365760"/>
+          <a:off x="3752850" y="365760"/>
           <a:ext cx="12700" cy="153035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4530,6 +4619,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4563,7 +4653,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="365760"/>
+          <a:off x="3752850" y="365760"/>
           <a:ext cx="141605" cy="13970"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4572,6 +4662,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4605,7 +4696,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4614,6 +4705,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4647,7 +4739,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4656,6 +4748,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4689,7 +4782,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4698,6 +4791,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4731,7 +4825,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4740,6 +4834,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4773,7 +4868,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4782,6 +4877,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4815,7 +4911,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4824,6 +4920,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4857,7 +4954,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4866,6 +4963,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4899,7 +4997,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4908,6 +5006,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4941,7 +5040,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4950,6 +5049,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -4983,7 +5083,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4992,6 +5092,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5025,7 +5126,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5034,6 +5135,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5067,7 +5169,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5076,6 +5178,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5109,7 +5212,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5118,6 +5221,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5151,7 +5255,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5160,6 +5264,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5193,7 +5298,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5202,6 +5307,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5235,7 +5341,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5244,6 +5350,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5277,7 +5384,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="12700" cy="151765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5286,6 +5393,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5319,7 +5427,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="0"/>
+          <a:off x="3752850" y="0"/>
           <a:ext cx="141605" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5328,6 +5436,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -5586,199 +5695,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr defaultColWidth="9.234375" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <cols>
+    <col min="37" max="37" width="14" style="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:36">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="28.8" customHeight="1" spans="1:37">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
     </row>
-    <row r="2" ht="42" customHeight="1" spans="1:36">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="42" customHeight="1" spans="1:37">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="11" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="3"/>
     </row>
-    <row r="3" spans="1:36">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:37">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AD3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="AH3" s="4" t="s">
+      <c r="AH3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AI3" s="4" t="s">
+      <c r="AI3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AJ3" s="4" t="s">
+      <c r="AJ3" s="9" t="s">
         <v>38</v>
+      </c>
+      <c r="AK3" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
